--- a/02-explore-with-pandas-solutions.xlsx
+++ b/02-explore-with-pandas-solutions.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -116,12 +116,53 @@
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="002A4365"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00718096"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00718096"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001A202C"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <name val="Consolas"/>
-      <color rgb="002E7D2E"/>
+      <color rgb="001A202C"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="002A4365"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00C53030"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <color rgb="002F6E2F"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -148,12 +189,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E6F3E6"/>
-        <bgColor rgb="00E6F3E6"/>
+        <fgColor rgb="002A4365"/>
+        <bgColor rgb="002A4365"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1EFE8"/>
+        <bgColor rgb="00F1EFE8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDF0F5"/>
+        <bgColor rgb="00EDF0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE7E7"/>
+        <bgColor rgb="00FCE7E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7F1E7"/>
+        <bgColor rgb="00E7F1E7"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -190,24 +255,52 @@
       </bottom>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="00D8DAE0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D8DAE0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D8DAE0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D8DAE0"/>
+      </bottom>
+    </border>
+    <border>
       <left style="medium">
-        <color rgb="002E7D2E"/>
+        <color rgb="002A4365"/>
       </left>
       <right style="medium">
-        <color rgb="002E7D2E"/>
+        <color rgb="002A4365"/>
       </right>
       <top style="medium">
-        <color rgb="002E7D2E"/>
+        <color rgb="002A4365"/>
       </top>
       <bottom style="medium">
-        <color rgb="002E7D2E"/>
+        <color rgb="002A4365"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002F6E2F"/>
+      </left>
+      <right style="medium">
+        <color rgb="002F6E2F"/>
+      </right>
+      <top style="medium">
+        <color rgb="002F6E2F"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002F6E2F"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -244,7 +337,33 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -658,7 +777,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00CF3338"/>
+    <tabColor rgb="002A4365"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -674,53 +793,53 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="20" t="inlineStr">
         <is>
           <t>Answer key — Explore with pandas</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="B2" s="11" t="inlineStr">
+    <row r="2" ht="40" customHeight="1">
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>ANSWER KEY for the workshop. Each step's green box shows the EXPECTED OUTPUT — what you should see when you run the code from column C in a PY() cell. To run the cells yourself, open 02-explore-with-pandas.xlsx (the unsolved version).</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>To insert a PY() cell:  press Ctrl + Alt + Shift + P  (or Formulas tab → Insert Python)</t>
+      <c r="B3" s="22" t="inlineStr">
+        <is>
+          <t>To insert a PY() cell:  Ctrl + Alt + Shift + P  (or Formulas tab → Insert Python)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Step 1 — Load the sales data</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>Read the 'sales' table into a DataFrame called sales_df. xl() is the bridge from worksheet to Python.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="50" customHeight="1">
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Code to run →</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="26" t="inlineStr">
         <is>
           <t>sales_df = xl("sales[#All]", headers=True)
 sales_df</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="30" t="inlineStr">
         <is>
           <t>✓ DataFrame loaded
 (200 rows, 7 columns)
@@ -730,53 +849,52 @@
     </row>
     <row r="8" ht="10" customHeight="1"/>
     <row r="9" ht="26" customHeight="1">
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>Step 2 — Peek at the data</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>Run each of these in its own PY() cell, stacked top-to-bottom in the red zone.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="92" customHeight="1">
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>Run each of these in its own PY() cell, stacked top-to-bottom in the blue zone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="78" customHeight="1">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>Code to run →</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="26" t="inlineStr">
         <is>
           <t>sales_df.head()</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="30" t="inlineStr">
         <is>
           <t>✓ first 5 rows
-ORD-0001 · Desk · Furniture · 68.76 · 5 · 37 · United States
-ORD-0002 · Lamp · Furniture · 115.20 · 7 · 24 · United States
+ORD-0001 · Desk · Furniture · 68.76 · 5 · 37 · US
+ORD-0002 · Lamp · Furniture · 115.20 · 7 · 24 · US
 ORD-0003 · Lamp · Furniture · 69.90 · 4 · 63 · Germany
-ORD-0004 · …
-ORD-0005 · …</t>
+…</t>
         </is>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Then try →</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="26" t="inlineStr">
         <is>
           <t>sales_df.tail()</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="E12" s="30" t="inlineStr">
         <is>
           <t>✓ last 5 rows
 (similar layout, rows 196–200)</t>
@@ -784,17 +902,17 @@
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>Then try →</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="26" t="inlineStr">
         <is>
           <t>sales_df.sample(5)</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="E13" s="30" t="inlineStr">
         <is>
           <t>✓ 5 random rows
 (different every run)</t>
@@ -802,17 +920,17 @@
       </c>
     </row>
     <row r="14" ht="36" customHeight="1">
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>Then try →</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t>sales_df.shape</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="E14" s="30" t="inlineStr">
         <is>
           <t>✓ dimensions
 (200, 7)</t>
@@ -821,31 +939,31 @@
     </row>
     <row r="15" ht="10" customHeight="1"/>
     <row r="16" ht="26" customHeight="1">
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>Step 3 — Summary stats and missing values</t>
         </is>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>describe() is your Analysis ToolPak replacement. isna().sum() finds gaps in each column.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="64" customHeight="1">
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>Code to run →</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C18" s="26" t="inlineStr">
         <is>
           <t>sales_df.describe()</t>
         </is>
       </c>
-      <c r="E18" s="20" t="inlineStr">
+      <c r="E18" s="30" t="inlineStr">
         <is>
           <t>✓ summary stats (numeric cols)
 unit_price → mean 211.95, std 215.73, min 2.17, max 760.69
@@ -855,56 +973,56 @@
       </c>
     </row>
     <row r="19" ht="120" customHeight="1">
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>Then try →</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C19" s="26" t="inlineStr">
         <is>
           <t>sales_df.isna().sum()</t>
         </is>
       </c>
-      <c r="E19" s="20" t="inlineStr">
+      <c r="E19" s="30" t="inlineStr">
         <is>
           <t>✓ missing per column
-order_id    0
-product     0
-category    0
-unit_price  0
-quantity    0
-customer_age 6  ← teaching moment
-country     0</t>
+order_id      0
+product       0
+category      0
+unit_price    0
+quantity      0
+customer_age  6  ← teaching moment
+country       0</t>
         </is>
       </c>
     </row>
     <row r="20" ht="10" customHeight="1"/>
     <row r="21" ht="26" customHeight="1">
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>Step 4 — Count categories</t>
         </is>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>value_counts() is a PivotTable for frequency in one line.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="92" customHeight="1">
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B23" s="25" t="inlineStr">
         <is>
           <t>Code to run →</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C23" s="26" t="inlineStr">
         <is>
           <t>sales_df['country'].value_counts()</t>
         </is>
       </c>
-      <c r="E23" s="20" t="inlineStr">
+      <c r="E23" s="30" t="inlineStr">
         <is>
           <t>✓ countries by frequency
 United States   77
@@ -916,17 +1034,17 @@
       </c>
     </row>
     <row r="24" ht="64" customHeight="1">
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B24" s="25" t="inlineStr">
         <is>
           <t>Then try →</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C24" s="26" t="inlineStr">
         <is>
           <t>sales_df['category'].value_counts(normalize=True)</t>
         </is>
       </c>
-      <c r="E24" s="20" t="inlineStr">
+      <c r="E24" s="30" t="inlineStr">
         <is>
           <t>✓ category proportions
 Office Supplies  0.40
@@ -937,88 +1055,88 @@
     </row>
     <row r="25" ht="10" customHeight="1"/>
     <row r="26" ht="26" customHeight="1">
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>Step 5 — Group and aggregate</t>
         </is>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B27" s="24" t="inlineStr">
         <is>
           <t>groupby() is a PivotTable in code. Split → apply → combine.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="92" customHeight="1">
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B28" s="25" t="inlineStr">
         <is>
           <t>Code to run →</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C28" s="26" t="inlineStr">
         <is>
           <t>sales_df.groupby('country')['unit_price'].mean()</t>
         </is>
       </c>
-      <c r="E28" s="20" t="inlineStr">
+      <c r="E28" s="30" t="inlineStr">
         <is>
           <t>✓ avg unit_price by country
-Australia       ~210
-Canada          ~225
-Germany         ~215
-UK              ~200
-United States   ~215</t>
+Australia        ~210
+Canada           ~225
+Germany          ~215
+United Kingdom   ~200
+United States    ~215</t>
         </is>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1">
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B29" s="25" t="inlineStr">
         <is>
           <t>Then try →</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C29" s="26" t="inlineStr">
         <is>
           <t>sales_df.groupby(['country','category'])['unit_price'].mean()</t>
         </is>
       </c>
-      <c r="E29" s="20" t="inlineStr">
+      <c r="E29" s="30" t="inlineStr">
         <is>
           <t>✓ avg by country × category
-(15 rows: each combination)</t>
+(15 rows — one per combination)</t>
         </is>
       </c>
     </row>
     <row r="30" ht="10" customHeight="1"/>
     <row r="31" ht="26" customHeight="1">
-      <c r="B31" s="13" t="inlineStr">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>Step 6 — Filter, group, sort (a chain)</t>
         </is>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1">
-      <c r="B32" s="14" t="inlineStr">
+      <c r="B32" s="24" t="inlineStr">
         <is>
           <t>Real analyst question: average unit price by category, US only, sorted high to low.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="64" customHeight="1">
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B33" s="25" t="inlineStr">
         <is>
           <t>Code to run →</t>
         </is>
       </c>
-      <c r="C33" s="16" t="inlineStr">
+      <c r="C33" s="26" t="inlineStr">
         <is>
           <t>us = sales_df[sales_df['country'] == 'United States']
 by_cat = us.groupby('category')['unit_price'].mean()
 by_cat.sort_values(ascending=False)</t>
         </is>
       </c>
-      <c r="E33" s="20" t="inlineStr">
+      <c r="E33" s="30" t="inlineStr">
         <is>
           <t>✓ US avg unit_price by category, sorted
 Electronics      → highest
@@ -1029,90 +1147,91 @@
     </row>
     <row r="34" ht="10" customHeight="1"/>
     <row r="35" ht="26" customHeight="1">
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>Step 7 — Add a revenue column</t>
         </is>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1">
-      <c r="B36" s="14" t="inlineStr">
+      <c r="B36" s="24" t="inlineStr">
         <is>
           <t>We'll use this in the chart in Step 8.</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="40" customHeight="1">
-      <c r="B37" s="15" t="inlineStr">
+    <row r="37" ht="50" customHeight="1">
+      <c r="B37" s="25" t="inlineStr">
         <is>
           <t>Code to run →</t>
         </is>
       </c>
-      <c r="C37" s="16" t="inlineStr">
+      <c r="C37" s="26" t="inlineStr">
         <is>
           <t>sales_df['revenue'] = sales_df['unit_price'] * sales_df['quantity']
 sales_df.head()</t>
         </is>
       </c>
-      <c r="E37" s="20" t="inlineStr">
+      <c r="E37" s="30" t="inlineStr">
         <is>
           <t>✓ revenue column added
-head() now shows 8 columns including revenue</t>
+sales_df.head() now shows 8 columns
+including revenue (unit_price × quantity)</t>
         </is>
       </c>
     </row>
     <row r="38" ht="10" customHeight="1"/>
     <row r="39" ht="26" customHeight="1">
-      <c r="B39" s="13" t="inlineStr">
+      <c r="B39" s="23" t="inlineStr">
         <is>
           <t>Step 8 — The chart that earns gasps</t>
         </is>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1">
-      <c r="B40" s="14" t="inlineStr">
+      <c r="B40" s="24" t="inlineStr">
         <is>
           <t>One line. Every numeric column correlated against every other. Toggle to Excel Value (Ctrl+Alt+Shift+M) to see the chart in the grid.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="92" customHeight="1">
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B41" s="25" t="inlineStr">
         <is>
           <t>Code to run →</t>
         </is>
       </c>
-      <c r="C41" s="16" t="inlineStr">
+      <c r="C41" s="26" t="inlineStr">
         <is>
           <t>import seaborn as sns
 sns.heatmap(
     sales_df.corr(numeric_only=True),
-    annot=True, cmap='RdGy_r', center=0
+    annot=True, cmap='RdBu_r', center=0
 )</t>
         </is>
       </c>
-      <c r="E41" s="20" t="inlineStr">
+      <c r="E41" s="30" t="inlineStr">
         <is>
           <t>✓ correlation heatmap
-4 × 4 matrix of correlations:
+4×4 matrix of correlations:
 unit_price ↔ revenue ≈ 0.84 (strong)
 quantity ↔ revenue ≈ 0.40
 others near 0
-(toggle to Excel Value to see the chart big)</t>
+(toggle to Excel Value to enlarge)</t>
         </is>
       </c>
     </row>
     <row r="42" ht="10" customHeight="1"/>
     <row r="43"/>
     <row r="44" ht="26" customHeight="1">
-      <c r="B44" s="18" t="inlineStr">
+      <c r="B44" s="28" t="inlineStr">
         <is>
           <t>⚠  Calc-order reminder</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="38" customHeight="1">
-      <c r="B45" s="19" t="inlineStr">
+    <row r="45" ht="48" customHeight="1">
+      <c r="B45" s="29" t="inlineStr">
         <is>
           <t>Each PY() cell can reference variables defined ABOVE or to the LEFT of it on this sheet. Build down the page — never up. If you see #PYTHON, your reference is probably above the cell that defines it.</t>
         </is>
